--- a/02_Mantenimiento_Industrial_limpio.xlsx
+++ b/02_Mantenimiento_Industrial_limpio.xlsx
@@ -971,7 +971,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>'temperatura' imputados con la mediana (73.2)</t>
+          <t>'temperatura' rellenos con la mediana (73.2)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'vibracion' imputados con la mediana (2.4)</t>
+          <t>'vibracion' rellenos con la mediana (2.4)</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>'presion' imputados con la mediana (8.3)</t>
+          <t>'presion' rellenos con la mediana (8.3)</t>
         </is>
       </c>
       <c r="C7" t="n">
